--- a/tests/build_food_db/fixtures/afcd_food_details_slice.xlsx
+++ b/tests/build_food_db/fixtures/afcd_food_details_slice.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Food Details" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contents" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Food details" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,246 +414,274 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Public Food Key</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Food Name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Food Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>F001234</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>24101</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Broccoli, fresh, raw</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Broccoli, fresh, raw</t>
+          <t>placeholder cover sheet</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Release 3 - Food details</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F001235</t>
+          <t>Public Food Key</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24304</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Carrot, mature, fresh, raw</t>
+          <t>Food Name</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Carrot, mature, fresh, peeled, raw</t>
+          <t>Food Description</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F001236</t>
+          <t>F001234</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24802</t>
+          <t>24101</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Potato, main crop, fresh, raw</t>
+          <t>Broccoli, fresh, raw</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Potato, main crop, fresh, peeled, raw</t>
+          <t>Broccoli, fresh, raw</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F002001</t>
+          <t>F001235</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>24304</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Apple, fresh, raw, unpeeled</t>
+          <t>Carrot, mature, fresh, raw</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apple, red varieties, fresh, raw, unpeeled</t>
+          <t>Carrot, mature, fresh, peeled, raw</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F002002</t>
+          <t>F001236</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>24802</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Banana, cavendish, fresh, raw</t>
+          <t>Potato, main crop, fresh, raw</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Banana, cavendish, fresh, peeled, raw</t>
+          <t>Potato, main crop, fresh, peeled, raw</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F003001</t>
+          <t>F002001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12201</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rice, white, polished, dry</t>
+          <t>Apple, fresh, raw, unpeeled</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Rice, white, long grain, polished, uncooked</t>
+          <t>Apple, red varieties, fresh, raw, unpeeled</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F004001</t>
+          <t>F002002</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Milk, cow, fluid, regular fat</t>
+          <t>Banana, cavendish, fresh, raw</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Milk, cow, fluid, regular fat (3.5%)</t>
+          <t>Banana, cavendish, fresh, peeled, raw</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F005001</t>
+          <t>F003001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>07101</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicken, breast, lean flesh, baked</t>
+          <t>Rice, white, polished, dry</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Chicken, breast, lean flesh, baked, no added fat</t>
+          <t>Rice, white, long grain, polished, uncooked</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F001240</t>
+          <t>F004001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24501</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spinach, fresh, raw</t>
+          <t>Milk, cow, fluid, regular fat</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Spinach, English, fresh, raw</t>
+          <t>Milk, cow, fluid, regular fat (3.5%)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>F005001</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>07101</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Chicken, breast, lean flesh, baked</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Chicken, breast, lean flesh, baked, no added fat</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F001240</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>24501</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Spinach, fresh, raw</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Spinach, English, fresh, raw</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>F006001</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>03101</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Bread, wholemeal, commercial</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Bread, wholemeal, sliced, commercial</t>
         </is>
